--- a/output/pdf_financials_xlsx/AROW.P.xlsx
+++ b/output/pdf_financials_xlsx/AROW.P.xlsx
@@ -2812,19 +2812,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.15418</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.15418</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.176934</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.176934</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.176934</v>
       </c>
     </row>
     <row r="93">
@@ -4162,7 +4162,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AROW.P.xlsx
+++ b/output/pdf_financials_xlsx/AROW.P.xlsx
@@ -658,10 +658,10 @@
         <v>0.01332</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.016505</v>
+        <v>0.06553</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.016111</v>
+        <v>0.053735</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.01785</v>
@@ -705,16 +705,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003855</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.024675</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.028272</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.015163</v>
       </c>
     </row>
     <row r="13">
@@ -1112,16 +1112,16 @@
         <v>-0.194355</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.022705</v>
+        <v>-0.02656</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.042277</v>
+        <v>-0.066952</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.026173</v>
+        <v>-0.054445</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.033921</v>
+        <v>-0.049084</v>
       </c>
     </row>
     <row r="28">
@@ -1162,16 +1162,16 @@
         <v>-0.194355</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.022705</v>
+        <v>-0.02656</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.042277</v>
+        <v>-0.066952</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.026173</v>
+        <v>-0.054445</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.033921</v>
+        <v>-0.049084</v>
       </c>
     </row>
     <row r="30">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.249289</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.916879</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.8997889999999999</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.249289</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.916879</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.8997889999999999</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>-0.06553</v>
+        <v>0.06553</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.053735</v>
+        <v>0.053735</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
